--- a/briefs/COMPETITOR_TENDER_MASTER_2026-10-12.xlsx
+++ b/briefs/COMPETITOR_TENDER_MASTER_2026-10-12.xlsx
@@ -34265,10 +34265,12 @@
           <t>Road quote Rs per tonne-km (YOUR NUMBER)</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n"/>
+      <c r="B3" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Type your tipper rate. Leave blank to use the illustrative rate.</t>
+          <t>Aman, chat 2026-10-12: approx Rs 5 per tonne per km (approximate, not a written quote). Clear the cell to fall back to the illustrative rate.</t>
         </is>
       </c>
     </row>

--- a/briefs/COMPETITOR_TENDER_MASTER_2026-10-12.xlsx
+++ b/briefs/COMPETITOR_TENDER_MASTER_2026-10-12.xlsx
@@ -502,7 +502,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Locations: mine and plant are matched from the tender title to the nearest listed town. Town coordinates were geocoded on 2026-10-12; the exact mine site is approximate [UNVERIFIED]. Reference point is Raigarh town until you name your siding's railway station (Settings).</t>
+          <t>Locations: mine and plant are matched from the tender title to the nearest listed town. Town coordinates were geocoded on 2026-10-12; the exact mine site is approximate [UNVERIFIED]. Reference point is Chaple, Kharsia block (your VWLR siding).</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G5" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v/>
       </c>
       <c r="V5" t="n">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="W5" s="6">
         <f>IF(ISNUMBER(V5),IF(V5*Settings!$B$8&gt;1000,"beyond table",IFERROR(LOOKUP(V5*Settings!$B$8,'FOIS 145A'!$A$2:$A$22,'FOIS 145A'!$C$2:$C$22)*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100)),"")),"")</f>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G7" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1338,80 +1338,83 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hemgir / Manoharpur (Sundargarh)</t>
+          <t>Dharamjaigarh (Raigarh)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hemgir / Manoharpur (Sundargarh)</t>
+          <t>Dharamjaigarh (Raigarh)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G8" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17034496</t>
+          <t>15913239</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026_OCAPL_127805_1</t>
+          <t>GEM/2025/B/6876204</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>transportation of coal from manoharpur coal mines to ntpc, darlipali, sundargarh by road</t>
+          <t>loading, transportation &amp; unloading and wagon loading of coal from surface coal yard of tlcmp to kchp</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Coal transport (road)</t>
+          <t>Coal transport (RCR / siding)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Odisha Coal And Power Limited</t>
+          <t>National Thermal Power Corporation Limited</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Orissa</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Sundergarh</t>
+          <t>Raigarh</t>
         </is>
       </c>
       <c r="O8" s="5" t="n">
-        <v>46121</v>
+        <v>45999</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>AOC</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>A B Carriers</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Vedvyas Logistic</t>
+          <t>Anoop Road Carriers, Mohit Minerals, Nkas Services, Orissa Stevedores</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>5 named / 5</t>
-        </is>
+          <t>5 named / 10</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>9.08</v>
       </c>
       <c r="U8" s="6">
         <f>IF(ISNUMBER(G8),MAX(MAX(G8,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -1438,96 +1441,83 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mine named in title; plant = tender city</t>
+          <t>mine named in title; plant = tender city in Maharashtra</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hemgir / Manoharpur (Sundargarh)</t>
+          <t>Dharamjaigarh (Raigarh)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Rourkela (tender city)</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>156</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14138047</t>
+          <t>14761268</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6302813</t>
+          <t>2025_NTPC_98502_1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>transportation of coal from ocpl manoharpur mines</t>
+          <t>coal transportation (20 lmt) from talaipalli mines to mouda stps under rcr mode via korichhapar siding</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Coal transport (road)</t>
+          <t>Coal transport (RCR / siding)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ntpc-Sail Power Company Private Limited</t>
+          <t>National Thermal Power Corporation Limited</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Orissa</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Rourkela</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="O9" s="5" t="n">
-        <v>45824</v>
+        <v>45870</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>AOC</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orissa Transport Co </t>
+          <t>-</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Anoop Road Carriers, Tirupati Minerals</t>
+          <t>Anoop Road Carriers, Godavari Commodities, Indermani / Indramani</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>4 named / 4</t>
-        </is>
-      </c>
-      <c r="T9" t="n">
-        <v>0.39</v>
+          <t>5 named / 20</t>
+        </is>
       </c>
       <c r="U9" s="6">
         <f>IF(ISNUMBER(G9),MAX(MAX(G9,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
         <v/>
       </c>
-      <c r="V9" t="n">
-        <v>156</v>
-      </c>
       <c r="W9" s="6">
         <f>IF(ISNUMBER(V9),IF(V9*Settings!$B$8&gt;1000,"beyond table",IFERROR(LOOKUP(V9*Settings!$B$8,'FOIS 145A'!$A$2:$A$22,'FOIS 145A'!$C$2:$C$22)*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100)),"")),"")</f>
         <v/>
@@ -1549,7 +1539,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mine named in title; plant = tender city</t>
+          <t>mine named in title; plant/siding named in title</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1558,32 +1548,32 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rourkela (tender city)</t>
+          <t>Sundargarh district (IB Valley / Hemgir)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>156</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13961330</t>
+          <t>17034496</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6196170</t>
+          <t>2026_OCAPL_127805_1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>transportation of coal from ocpl manoharpur mines to any private/public s</t>
+          <t>transportation of coal from manoharpur coal mines to ntpc, darlipali, sundargarh by road</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1593,7 +1583,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ntpc-Sail Power Company Private Limited</t>
+          <t>Odisha Coal And Power Limited</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1603,15 +1593,15 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Rourkela</t>
+          <t>Sundergarh</t>
         </is>
       </c>
       <c r="O10" s="5" t="n">
-        <v>45810</v>
+        <v>46121</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1621,21 +1611,18 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Advika Logistics, Anoop Road Carriers, Godavari Commodities</t>
+          <t>Vedvyas Logistic</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>5 named / 20</t>
+          <t>5 named / 5</t>
         </is>
       </c>
       <c r="U10" s="6">
         <f>IF(ISNUMBER(G10),MAX(MAX(G10,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
         <v/>
       </c>
-      <c r="V10" t="n">
-        <v>156</v>
-      </c>
       <c r="W10" s="6">
         <f>IF(ISNUMBER(V10),IF(V10*Settings!$B$8&gt;1000,"beyond table",IFERROR(LOOKUP(V10*Settings!$B$8,'FOIS 145A'!$A$2:$A$22,'FOIS 145A'!$C$2:$C$22)*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100)),"")),"")</f>
         <v/>
@@ -1657,41 +1644,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mine named in title; plant = tender city</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Hemgir / Manoharpur (Sundargarh)</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>32</v>
-      </c>
+          <t>plant/siding named in title</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rourkela (tender city)</t>
+          <t>Dharamjaigarh (Raigarh)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>156</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13168942</t>
+          <t>16814789</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6073786</t>
+          <t>GEM/2026/B/7315717</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>transportation of coal from ocpl manoharpur mines to any privatepublic si</t>
+          <t>coal transportation from ramnagore colliery to nspcl durgapur</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1706,16 +1686,16 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Orissa</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Rourkela</t>
+          <t>Durgapur</t>
         </is>
       </c>
       <c r="O11" s="5" t="n">
-        <v>45750</v>
+        <v>46097</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1724,29 +1704,26 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Alps Mining Services Private Limited</t>
+          <t>M/S United Coal Carriers</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Anoop Road Carriers, Tirupati Minerals</t>
+          <t>United Coal Carriers</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>3 named / 3</t>
+          <t>5 named / 5</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>0.4</v>
+        <v>0.21</v>
       </c>
       <c r="U11" s="6">
         <f>IF(ISNUMBER(G11),MAX(MAX(G11,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
         <v/>
       </c>
-      <c r="V11" t="n">
-        <v>156</v>
-      </c>
       <c r="W11" s="6">
         <f>IF(ISNUMBER(V11),IF(V11*Settings!$B$8&gt;1000,"beyond table",IFERROR(LOOKUP(V11*Settings!$B$8,'FOIS 145A'!$A$2:$A$22,'FOIS 145A'!$C$2:$C$22)*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100)),"")),"")</f>
         <v/>
@@ -1768,51 +1745,51 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mine = coal company's tender city; siding = same area</t>
+          <t>mine named in title; plant = tender city</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sundargarh district (IB Valley / Hemgir) (tender city)</t>
+          <t>Hemgir / Manoharpur (Sundargarh)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sundargarh district (IB Valley / Hemgir) (tender city)</t>
+          <t>Rourkela (tender city)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="G12" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>12921764</t>
+          <t>14138047</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>GEM/2025/B/5954457</t>
+          <t>GEM/2025/B/6302813</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>loading of road sale tippe</t>
+          <t>transportation of coal from ocpl manoharpur mines</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Loading / handling / crushing</t>
+          <t>Coal transport (road)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Mahanadi Coalfields Limited</t>
+          <t>Ntpc-Sail Power Company Private Limited</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1822,11 +1799,11 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Sundergarh</t>
+          <t>Rourkela</t>
         </is>
       </c>
       <c r="O12" s="5" t="n">
-        <v>45719</v>
+        <v>45824</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1835,22 +1812,29 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Millennium Suppliers Private Limited</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
+          <t xml:space="preserve">Orissa Transport Co </t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Anoop Road Carriers, Tirupati Minerals</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>5 named / 12</t>
+          <t>4 named / 4</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>26.98</v>
+        <v>0.39</v>
       </c>
       <c r="U12" s="6">
         <f>IF(ISNUMBER(G12),MAX(MAX(G12,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
         <v/>
       </c>
+      <c r="V12" t="n">
+        <v>174</v>
+      </c>
       <c r="W12" s="6">
         <f>IF(ISNUMBER(V12),IF(V12*Settings!$B$8&gt;1000,"beyond table",IFERROR(LOOKUP(V12*Settings!$B$8,'FOIS 145A'!$A$2:$A$22,'FOIS 145A'!$C$2:$C$22)*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100)),"")),"")</f>
         <v/>
@@ -1872,51 +1856,51 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mine = coal company's tender city; siding = same area</t>
+          <t>mine named in title; plant = tender city</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sundargarh district (IB Valley / Hemgir) (tender city)</t>
+          <t>Hemgir / Manoharpur (Sundargarh)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sundargarh district (IB Valley / Hemgir) (tender city)</t>
+          <t>Rourkela (tender city)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="G13" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15025805</t>
+          <t>13961330</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6419957</t>
+          <t>GEM/2025/B/6196170</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>hiring of pay loaders and</t>
+          <t>transportation of coal from ocpl manoharpur mines to any private/public s</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Coal transport (road)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Mahanadi Coalfields Limited</t>
+          <t>Ntpc-Sail Power Company Private Limited</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1926,39 +1910,39 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Sundergarh</t>
+          <t>Rourkela</t>
         </is>
       </c>
       <c r="O13" s="5" t="n">
-        <v>45859</v>
+        <v>45810</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>AOC</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Matarani Resources Private Limited</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Saikrupa Coal Supplier</t>
+          <t>Advika Logistics, Anoop Road Carriers, Godavari Commodities</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3 named / 3</t>
-        </is>
-      </c>
-      <c r="T13" t="n">
-        <v>7.1</v>
+          <t>5 named / 20</t>
+        </is>
       </c>
       <c r="U13" s="6">
         <f>IF(ISNUMBER(G13),MAX(MAX(G13,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
         <v/>
       </c>
+      <c r="V13" t="n">
+        <v>174</v>
+      </c>
       <c r="W13" s="6">
         <f>IF(ISNUMBER(V13),IF(V13*Settings!$B$8&gt;1000,"beyond table",IFERROR(LOOKUP(V13*Settings!$B$8,'FOIS 145A'!$A$2:$A$22,'FOIS 145A'!$C$2:$C$22)*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100)),"")),"")</f>
         <v/>
@@ -1980,51 +1964,51 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mine = coal company's tender city; siding = same area</t>
+          <t>mine named in title; plant = tender city</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sundargarh district (IB Valley / Hemgir) (tender city)</t>
+          <t>Hemgir / Manoharpur (Sundargarh)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sundargarh district (IB Valley / Hemgir) (tender city)</t>
+          <t>Rourkela (tender city)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="G14" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14395678</t>
+          <t>13168942</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6315435</t>
+          <t>GEM/2025/B/6073786</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>extraction of coal/coal me</t>
+          <t>transportation of coal from ocpl manoharpur mines to any privatepublic si</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Coal transport (road)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Mahanadi Coalfields Limited</t>
+          <t>Ntpc-Sail Power Company Private Limited</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2034,11 +2018,11 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Sundergarh</t>
+          <t>Rourkela</t>
         </is>
       </c>
       <c r="O14" s="5" t="n">
-        <v>45848</v>
+        <v>45750</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -2047,22 +2031,29 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Shree Ranisati Mining</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
+          <t>Alps Mining Services Private Limited</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Anoop Road Carriers, Tirupati Minerals</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>5 named / 9</t>
+          <t>3 named / 3</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>174.14</v>
+        <v>0.4</v>
       </c>
       <c r="U14" s="6">
         <f>IF(ISNUMBER(G14),MAX(MAX(G14,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
         <v/>
       </c>
+      <c r="V14" t="n">
+        <v>174</v>
+      </c>
       <c r="W14" s="6">
         <f>IF(ISNUMBER(V14),IF(V14*Settings!$B$8&gt;1000,"beyond table",IFERROR(LOOKUP(V14*Settings!$B$8,'FOIS 145A'!$A$2:$A$22,'FOIS 145A'!$C$2:$C$22)*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100)),"")),"")</f>
         <v/>
@@ -2093,7 +2084,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2101,29 +2092,29 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>13393053</t>
+          <t>12921764</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6129453</t>
+          <t>GEM/2025/B/5954457</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>hiring of pay loaders &amp; ti</t>
+          <t>loading of road sale tippe</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Loading / handling / crushing</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2142,7 +2133,7 @@
         </is>
       </c>
       <c r="O15" s="5" t="n">
-        <v>45772</v>
+        <v>45719</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -2151,17 +2142,17 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Vansh Logistics</t>
+          <t>Millennium Suppliers Private Limited</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>5 named / 9</t>
+          <t>5 named / 12</t>
         </is>
       </c>
       <c r="T15" t="n">
-        <v>41.46</v>
+        <v>26.98</v>
       </c>
       <c r="U15" s="6">
         <f>IF(ISNUMBER(G15),MAX(MAX(G15,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -2188,58 +2179,58 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>plant = tender city</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Sundargarh district (IB Valley / Hemgir) (tender city)</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>32</v>
-      </c>
+          <t>mine named in title</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Dharamjaigarh (Raigarh)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>53</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12797284</t>
+          <t>17065555</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>GEM/2025/B/5848728</t>
+          <t>GEM/2026/B/7067958</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>providing assistance for om activities at ntpc dlcmp</t>
+          <t>handling service, handling &amp; transport service, ob removal, coal extraction, composite work for ob removal cutting loading transportation wagon loading of coal at durgapur ocm r..</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Mining services (OB / extraction)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>National Thermal Power Corporation Limited</t>
+          <t>South Eastern Coalfields Limited</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Orissa</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Sundergarh</t>
+          <t>Raigarh</t>
         </is>
       </c>
       <c r="O16" s="5" t="n">
-        <v>45713</v>
+        <v>46081</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -2248,17 +2239,17 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>M/S A P Construction</t>
+          <t>Sunil Kumar Agrawal</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>5 named / 9</t>
+          <t>5 named / 11</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>2.19</v>
+        <v>4247.08</v>
       </c>
       <c r="U16" s="6">
         <f>IF(ISNUMBER(G16),MAX(MAX(G16,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -2285,78 +2276,88 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mine named in title</t>
+          <t>mine = coal company's tender city; siding = same area</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IB Valley (Jharsuguda)</t>
+          <t>Sundargarh district (IB Valley / Hemgir) (tender city)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sundargarh district (IB Valley / Hemgir) (tender city)</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>53</v>
+      </c>
       <c r="G17" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>18286647</t>
+          <t>15025805</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026_NTPC_111971_1</t>
+          <t>GEM/2025/B/6419957</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>contract for loading and transportation of coal from mcl-ib mine to any designated siding and loading in indian railway wagons for onward transportation to ntpc simhadri.</t>
+          <t>hiring of pay loaders and</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Coal transport (RCR / siding)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>National Thermal Power Corporation Limited</t>
+          <t>Mahanadi Coalfields Limited</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Orissa</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Visakhapatnam</t>
+          <t>Sundergarh</t>
         </is>
       </c>
       <c r="O17" s="5" t="n">
-        <v>46274</v>
+        <v>45859</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AOC</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Matarani Resources Private Limited</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Anoop Road Carriers, Bharat Road Carrier, Sangita Sales, Swami Fuels</t>
+          <t>Saikrupa Coal Supplier</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>5 named / 6</t>
-        </is>
+          <t>3 named / 3</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>7.1</v>
       </c>
       <c r="U17" s="6">
         <f>IF(ISNUMBER(G17),MAX(MAX(G17,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -2388,41 +2389,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brajrajnagar / Jharsuguda (tender city)</t>
+          <t>Sundargarh district (IB Valley / Hemgir) (tender city)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brajrajnagar / Jharsuguda (tender city)</t>
+          <t>Sundargarh district (IB Valley / Hemgir) (tender city)</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>12706783</t>
+          <t>14395678</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>GEM/2025/B/5868534</t>
+          <t>GEM/2025/B/6315435</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>loading and transportation</t>
+          <t>extraction of coal/coal me</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Coal transport (road)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2437,11 +2438,11 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Jharsuguda</t>
+          <t>Sundergarh</t>
         </is>
       </c>
       <c r="O18" s="5" t="n">
-        <v>45708</v>
+        <v>45848</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2450,17 +2451,17 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Variant Commercial Private Limited</t>
+          <t>Shree Ranisati Mining</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>5 named / 11</t>
+          <t>5 named / 9</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>94.20999999999999</v>
+        <v>174.14</v>
       </c>
       <c r="U18" s="6">
         <f>IF(ISNUMBER(G18),MAX(MAX(G18,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -2487,78 +2488,84 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mine named in title</t>
+          <t>mine = coal company's tender city; siding = same area</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Talabira (near Sambalpur/Jharsuguda)</t>
+          <t>Sundargarh district (IB Valley / Hemgir) (tender city)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>61</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sundargarh district (IB Valley / Hemgir) (tender city)</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>53</v>
+      </c>
       <c r="G19" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18306349</t>
+          <t>13393053</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026_NTPC_111933_1</t>
+          <t>GEM/2025/B/6129453</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>transportation of 2 lmt coal from nlc talabira mines to ntpc simhadri through rcr mode - as per sow</t>
+          <t>hiring of pay loaders &amp; ti</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Coal transport (RCR / siding)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>National Thermal Power Corporation Limited</t>
+          <t>Mahanadi Coalfields Limited</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Orissa</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Raipur</t>
+          <t>Sundergarh</t>
         </is>
       </c>
       <c r="O19" s="5" t="n">
-        <v>46288</v>
+        <v>45772</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AOC</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Anoop Road Carriers, Bharat Road Carrier, Mohit Minerals, Sangita Sales</t>
-        </is>
-      </c>
+          <t>Vansh Logistics</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>5 named / 8</t>
-        </is>
+          <t>5 named / 9</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>41.46</v>
       </c>
       <c r="U19" s="6">
         <f>IF(ISNUMBER(G19),MAX(MAX(G19,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -2585,46 +2592,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mine named in title; plant/siding named in title</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Talabira (near Sambalpur/Jharsuguda)</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>61</v>
-      </c>
+          <t>plant = tender city</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Talabira (near Sambalpur/Jharsuguda)</t>
+          <t>Sundargarh district (IB Valley / Hemgir) (tender city)</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G20" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>18286732</t>
+          <t>12797284</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026_NTPC_111957_1</t>
+          <t>GEM/2025/B/5848728</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>coal transportation from nlc talabira mines to ntpc telangana(ttgr) - coal transportation from nlc talabira mines to ntpc telangana(ttgr)through rcr mode</t>
+          <t>providing assistance for om activities at ntpc dlcmp</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Coal transport (RCR / siding)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2634,16 +2634,16 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Orissa</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Raipur</t>
+          <t>Sundergarh</t>
         </is>
       </c>
       <c r="O20" s="5" t="n">
-        <v>46287</v>
+        <v>45713</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2652,21 +2652,17 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Swami Fuels Private Limited</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Anoop Road Carriers, Swami Fuels, Tirupati Minerals</t>
-        </is>
-      </c>
+          <t>M/S A P Construction</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>4 named / 4</t>
+          <t>5 named / 9</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>6.68</v>
+        <v>2.19</v>
       </c>
       <c r="U20" s="6">
         <f>IF(ISNUMBER(G20),MAX(MAX(G20,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -2693,34 +2689,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mine named in title</t>
+          <t>mine = coal company's tender city; siding = same area</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Talabira (near Sambalpur/Jharsuguda)</t>
+          <t>Korba (tender city)</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Korba (tender city)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>65</v>
+      </c>
       <c r="G21" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>18222478</t>
+          <t>16687336</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026_NTPC_111805_1</t>
+          <t>GEM/2025/B/7005420</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>coal transportation from nlc talabira mines to ntpc kudgi through rcr</t>
+          <t>handling &amp; transport service, transport service, handling service, hiring of pay loader and tippers for coal loading at saraipali transportation and loading into wagons at korba..</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2730,21 +2733,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>National Thermal Power Corporation Limited</t>
+          <t>South Eastern Coalfields Limited</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Kudligi</t>
+          <t>Korba</t>
         </is>
       </c>
       <c r="O21" s="5" t="n">
-        <v>46156</v>
+        <v>46024</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2753,17 +2756,21 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Kalyani Ventures Limited</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
+          <t>G K Associates</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>G K Associates</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1 named / 1</t>
+          <t>5 named / 30</t>
         </is>
       </c>
       <c r="T21" t="n">
-        <v>1.5</v>
+        <v>329.87</v>
       </c>
       <c r="U21" s="6">
         <f>IF(ISNUMBER(G21),MAX(MAX(G21,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -2790,34 +2797,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>mine named in title; plant = tender city in West Bengal</t>
+          <t>mine named in title; plant/siding named in title</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Talabira (near Sambalpur/Jharsuguda)</t>
+          <t>Korba</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>61</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Korba</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>65</v>
+      </c>
       <c r="G22" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>15407506</t>
+          <t>16125779</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2025_DVC_245419_1</t>
+          <t>GEM/2025/B/6972824</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>lifting of 20.0(twenty) lmt coal from nlc india limited (nlcil)-talabira ii and iii ocp, sambalpur, odisha to dstps and other tps of dvc through rcr mode</t>
+          <t>handling &amp; transport service, coal loading &amp; transportation from saraipali ocm to srk rl siding, korba</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2827,41 +2841,44 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Damodar Valley Corporation</t>
+          <t>South Eastern Coalfields Limited</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Korba</t>
         </is>
       </c>
       <c r="O22" s="5" t="n">
-        <v>45897</v>
+        <v>46013</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>AOC</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M/S Chandan Kumar Singh</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Anoop Road Carriers, Godavari Commodities</t>
+          <t>G K Associates, Chandan Kumar Singh</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>5 named / 17</t>
-        </is>
+          <t>5 named / 7</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>1.58</v>
       </c>
       <c r="U22" s="6">
         <f>IF(ISNUMBER(G22),MAX(MAX(G22,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -2893,73 +2910,72 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Talabira (near Sambalpur/Jharsuguda)</t>
+          <t>Korba</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14761261</t>
+          <t>16687380</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2025_NTPC_98583_1</t>
+          <t>GEM/2026/B/7114126</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>transportation of 300000mt coal from nlc talabira mines of nlc ltd to ntpc simhadri under rcr mode through any nearby siding</t>
+          <t>hiring of pay loaders and tippers for mechanical loading and transportation of coal at dipka oc expansion project, dipka area, secl for a period of 1096 days</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Coal transport (RCR / siding)</t>
+          <t>Coal transport (road)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>National Thermal Power Corporation Limited</t>
+          <t>South Eastern Coalfields Limited</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Visakhapatnam</t>
+          <t>Korba</t>
         </is>
       </c>
       <c r="O23" s="5" t="n">
-        <v>45880</v>
+        <v>46053</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>AOC</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Advika Logistics, Anoop Road Carriers, Indermani / Indramani</t>
-        </is>
-      </c>
+          <t>Maa Parwati Transport</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>5 named / 15</t>
-        </is>
+          <t>5 named / 9</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>90.23999999999999</v>
       </c>
       <c r="U23" s="6">
         <f>IF(ISNUMBER(G23),MAX(MAX(G23,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -2986,51 +3002,44 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>mine named in title; plant/siding named in title</t>
+          <t>mine named in title</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dharamjaigarh (Raigarh)</t>
+          <t>Korba</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>66</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Dharamjaigarh (Raigarh)</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>66</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>15913239</t>
+          <t>16786403</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6876204</t>
+          <t>GEM/2025/B/6972482</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>loading, transportation &amp; unloading and wagon loading of coal from surface coal yard of tlcmp to kchp</t>
+          <t>hiring of pay loader, mobile crusher and tippers for transportation of coal at gevra area secl</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Coal transport (RCR / siding)</t>
+          <t>Coal transport (road)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>National Thermal Power Corporation Limited</t>
+          <t>South Eastern Coalfields Limited</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3040,11 +3049,11 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Raigarh</t>
+          <t>Korba</t>
         </is>
       </c>
       <c r="O24" s="5" t="n">
-        <v>45999</v>
+        <v>46023</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -3053,21 +3062,21 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>A B Carriers</t>
+          <t>Vikas Coal And Minerals Private Limited</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Anoop Road Carriers, Mohit Minerals, Nkas Services, Orissa Stevedores</t>
+          <t>G K Associates</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>5 named / 10</t>
+          <t>5 named / 16</t>
         </is>
       </c>
       <c r="T24" t="n">
-        <v>9.08</v>
+        <v>140.8</v>
       </c>
       <c r="U24" s="6">
         <f>IF(ISNUMBER(G24),MAX(MAX(G24,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -3094,78 +3103,88 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>mine named in title; plant = tender city in Maharashtra</t>
+          <t>mine = coal company's tender city; siding = same area</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dharamjaigarh (Raigarh)</t>
+          <t>Korba (tender city)</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>66</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Korba (tender city)</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>65</v>
+      </c>
       <c r="G25" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14761268</t>
+          <t>15830605</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2025_NTPC_98502_1</t>
+          <t>GEM/2025/B/6869302</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>coal transportation (20 lmt) from talaipalli mines to mouda stps under rcr mode via korichhapar siding</t>
+          <t>loading and transportation of coal</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Coal transport (RCR / siding)</t>
+          <t>Coal transport (road)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>National Thermal Power Corporation Limited</t>
+          <t>South Eastern Coalfields Limited</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Korba</t>
         </is>
       </c>
       <c r="O25" s="5" t="n">
-        <v>45870</v>
+        <v>45989</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AOC</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>G K Associates</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Anoop Road Carriers, Godavari Commodities, Indermani / Indramani</t>
+          <t>G K Associates</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>5 named / 20</t>
-        </is>
+          <t>3 named / 3</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>1.67</v>
       </c>
       <c r="U25" s="6">
         <f>IF(ISNUMBER(G25),MAX(MAX(G25,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -3192,34 +3211,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>plant/siding named in title</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>mine = coal company's tender city; siding = same area</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Korba (tender city)</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>65</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dharamjaigarh (Raigarh)</t>
+          <t>Korba (tender city)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G26" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>16814789</t>
+          <t>14287776</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>GEM/2026/B/7315717</t>
+          <t>GEM/2025/B/6337006</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>coal transportation from ramnagore colliery to nspcl durgapur</t>
+          <t>loading and transportation</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3229,21 +3255,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ntpc-Sail Power Company Private Limited</t>
+          <t>South Eastern Coalfields Limited</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Durgapur</t>
+          <t>Korba</t>
         </is>
       </c>
       <c r="O26" s="5" t="n">
-        <v>46097</v>
+        <v>45836</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3252,21 +3278,21 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>M/S United Coal Carriers</t>
+          <t>Rakesh Kumar Enterprises</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>United Coal Carriers</t>
+          <t>G K Associates</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>5 named / 5</t>
+          <t>5 named / 6</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>0.21</v>
+        <v>1.9</v>
       </c>
       <c r="U26" s="6">
         <f>IF(ISNUMBER(G26),MAX(MAX(G26,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -3298,34 +3324,34 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dharamjaigarh (Raigarh)</t>
+          <t>Korba</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>17065555</t>
+          <t>17670369</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>GEM/2026/B/7067958</t>
+          <t>GEM/2026/B/7435893</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>handling service, handling &amp; transport service, ob removal, coal extraction, composite work for ob removal cutting loading transportation wagon loading of coal at durgapur ocm r..</t>
+          <t>handling service, excavator with crusher bucket system with screening and loading of coal into tippers at kusmunda oc kusmunda area</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Mining services (OB / extraction)</t>
+          <t>Loading / handling / crushing</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3340,11 +3366,11 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Raigarh</t>
+          <t>Korba</t>
         </is>
       </c>
       <c r="O27" s="5" t="n">
-        <v>46081</v>
+        <v>46156</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -3353,17 +3379,17 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Sunil Kumar Agrawal</t>
+          <t>Fsnl Private Limited, Maa Sarwamangla Transport Company</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>5 named / 11</t>
+          <t>5 named / 8</t>
         </is>
       </c>
       <c r="T27" t="n">
-        <v>4247.08</v>
+        <v>24.94</v>
       </c>
       <c r="U27" s="6">
         <f>IF(ISNUMBER(G27),MAX(MAX(G27,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -3395,60 +3421,60 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sambalpur (tender city)</t>
+          <t>Korba (tender city)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sambalpur (tender city)</t>
+          <t>Korba (tender city)</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="G28" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>12395907</t>
+          <t>15659451</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>GEM/2024/B/5759091</t>
+          <t>GEM/2025/B/6627991</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>coal loading and transport</t>
+          <t>handling service, transpor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Coal transport (road)</t>
+          <t>Loading / handling / crushing</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Mahanadi Coalfields Limited</t>
+          <t>South Eastern Coalfields Limited</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Orissa</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Sambalpur</t>
+          <t>Korba</t>
         </is>
       </c>
       <c r="O28" s="5" t="n">
-        <v>45670</v>
+        <v>45923</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -3457,17 +3483,21 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Vlt Associates</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
+          <t>Harsh Roadlines Private Limited</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Orissa Stevedores</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>5 named / 10</t>
+          <t>5 named / 8</t>
         </is>
       </c>
       <c r="T28" t="n">
-        <v>28</v>
+        <v>82.78</v>
       </c>
       <c r="U28" s="6">
         <f>IF(ISNUMBER(G28),MAX(MAX(G28,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -3503,7 +3533,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -3511,29 +3541,29 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="G29" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>16687336</t>
+          <t>17304517</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>GEM/2025/B/7005420</t>
+          <t>GEM/2026/B/7372908</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>handling &amp; transport service, transport service, handling service, hiring of pay loader and tippers for coal loading at saraipali transportation and loading into wagons at korba..</t>
+          <t>handling service, transport service, handling &amp; transport service, ob removal, composite work for ob removal coal cutting by surface miner and loading and transportation of coal..</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Coal transport (RCR / siding)</t>
+          <t>Mining services (OB / extraction)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3552,7 +3582,7 @@
         </is>
       </c>
       <c r="O29" s="5" t="n">
-        <v>46024</v>
+        <v>46135</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -3561,21 +3591,17 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>G K Associates</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>G K Associates</t>
-        </is>
-      </c>
+          <t>Knr Constructions Limited</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>5 named / 30</t>
+          <t>5 named / 8</t>
         </is>
       </c>
       <c r="T29" t="n">
-        <v>329.87</v>
+        <v>3966.12</v>
       </c>
       <c r="U29" s="6">
         <f>IF(ISNUMBER(G29),MAX(MAX(G29,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -3602,7 +3628,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>mine named in title; plant/siding named in title</t>
+          <t>mine named in title</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3611,56 +3637,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>88</v>
-      </c>
-      <c r="E30" t="inlineStr">
+        <v>65</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>65</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>16765105</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>GEM/2025/B/7003673</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ob removal, handling &amp; transport service, hiring of hemm for ob removal and coal drilling with loading and transportation at manikpur ocp korba area</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Mining services (OB / extraction)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>South Eastern Coalfields Limited</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>Korba</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>88</v>
-      </c>
-      <c r="G30" t="n">
-        <v>88</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>16125779</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>GEM/2025/B/6972824</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>handling &amp; transport service, coal loading &amp; transportation from saraipali ocm to srk rl siding, korba</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Coal transport (RCR / siding)</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>South Eastern Coalfields Limited</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Chhattisgarh</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Korba</t>
-        </is>
-      </c>
       <c r="O30" s="5" t="n">
-        <v>46013</v>
+        <v>46043</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3669,21 +3688,17 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>M/S Chandan Kumar Singh</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>G K Associates, Chandan Kumar Singh</t>
-        </is>
-      </c>
+          <t>Orissa Stevedores Limited</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>5 named / 7</t>
+          <t>5 named / 10</t>
         </is>
       </c>
       <c r="T30" t="n">
-        <v>1.58</v>
+        <v>1775.85</v>
       </c>
       <c r="U30" s="6">
         <f>IF(ISNUMBER(G30),MAX(MAX(G30,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -3710,58 +3725,65 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>mine named in title</t>
+          <t>mine = coal company's tender city; siding = same area</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Korba (tender city)</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>65</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Korba (tender city)</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>65</v>
+      </c>
+      <c r="G31" t="n">
+        <v>65</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>16245601</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>GEM/2025/B/6729097</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>hiring of pay loader incorporated with weight sensors for mechanical transfer of coal into railway wagons for a quantity of 17520000 te with minimum tpd16000 te for a period of ..</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>South Eastern Coalfields Limited</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>Korba</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>88</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="G31" t="n">
-        <v>88</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>16687380</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>GEM/2026/B/7114126</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>hiring of pay loaders and tippers for mechanical loading and transportation of coal at dipka oc expansion project, dipka area, secl for a period of 1096 days</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Coal transport (road)</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>South Eastern Coalfields Limited</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Chhattisgarh</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Korba</t>
-        </is>
-      </c>
       <c r="O31" s="5" t="n">
-        <v>46053</v>
+        <v>45948</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3770,17 +3792,17 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Maa Parwati Transport</t>
+          <t>Sat Kartar Logistics</t>
         </is>
       </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>5 named / 9</t>
+          <t>5 named / 19</t>
         </is>
       </c>
       <c r="T31" t="n">
-        <v>90.23999999999999</v>
+        <v>14.89</v>
       </c>
       <c r="U31" s="6">
         <f>IF(ISNUMBER(G31),MAX(MAX(G31,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -3807,58 +3829,65 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>mine named in title</t>
+          <t>mine = coal company's tender city; siding = same area</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>Korba (tender city)</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>65</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Korba (tender city)</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>65</v>
+      </c>
+      <c r="G32" t="n">
+        <v>65</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>12743621</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>GEM/2025/B/5926593</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>hiring of payloaders and t</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>South Eastern Coalfields Limited</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>Korba</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>88</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="G32" t="n">
-        <v>88</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>16786403</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>GEM/2025/B/6972482</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>hiring of pay loader, mobile crusher and tippers for transportation of coal at gevra area secl</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Coal transport (road)</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>South Eastern Coalfields Limited</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Chhattisgarh</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Korba</t>
-        </is>
-      </c>
       <c r="O32" s="5" t="n">
-        <v>46023</v>
+        <v>45712</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -3867,21 +3896,17 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Vikas Coal And Minerals Private Limited</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>G K Associates</t>
-        </is>
-      </c>
+          <t>Harsh Roadlines Private Limited</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>5 named / 16</t>
+          <t>5 named / 7</t>
         </is>
       </c>
       <c r="T32" t="n">
-        <v>140.8</v>
+        <v>2.41</v>
       </c>
       <c r="U32" s="6">
         <f>IF(ISNUMBER(G32),MAX(MAX(G32,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -3908,88 +3933,78 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>mine = coal company's tender city; siding = same area</t>
+          <t>mine named in title</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Korba (tender city)</t>
+          <t>IB Valley (Jharsuguda)</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>88</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Korba (tender city)</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>88</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>15830605</t>
+          <t>18286647</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6869302</t>
+          <t>2026_NTPC_111971_1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>loading and transportation of coal</t>
+          <t>contract for loading and transportation of coal from mcl-ib mine to any designated siding and loading in indian railway wagons for onward transportation to ntpc simhadri.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Coal transport (road)</t>
+          <t>Coal transport (RCR / siding)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>South Eastern Coalfields Limited</t>
+          <t>National Thermal Power Corporation Limited</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Korba</t>
+          <t>Visakhapatnam</t>
         </is>
       </c>
       <c r="O33" s="5" t="n">
-        <v>45989</v>
+        <v>46274</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>AOC</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>G K Associates</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>G K Associates</t>
+          <t>Anoop Road Carriers, Bharat Road Carrier, Sangita Sales, Swami Fuels</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>3 named / 3</t>
-        </is>
-      </c>
-      <c r="T33" t="n">
-        <v>1.67</v>
+          <t>5 named / 6</t>
+        </is>
       </c>
       <c r="U33" s="6">
         <f>IF(ISNUMBER(G33),MAX(MAX(G33,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -4021,31 +4036,31 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Korba (tender city)</t>
+          <t>Brajrajnagar / Jharsuguda (tender city)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Korba (tender city)</t>
+          <t>Brajrajnagar / Jharsuguda (tender city)</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G34" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>14287776</t>
+          <t>12706783</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6337006</t>
+          <t>GEM/2025/B/5868534</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4060,21 +4075,21 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>South Eastern Coalfields Limited</t>
+          <t>Mahanadi Coalfields Limited</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Orissa</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Korba</t>
+          <t>Jharsuguda</t>
         </is>
       </c>
       <c r="O34" s="5" t="n">
-        <v>45836</v>
+        <v>45708</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -4083,21 +4098,17 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Rakesh Kumar Enterprises</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>G K Associates</t>
-        </is>
-      </c>
+          <t>Variant Commercial Private Limited</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>5 named / 6</t>
+          <t>5 named / 11</t>
         </is>
       </c>
       <c r="T34" t="n">
-        <v>1.9</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="U34" s="6">
         <f>IF(ISNUMBER(G34),MAX(MAX(G34,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -4129,39 +4140,39 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Korba</t>
+          <t>Talabira (near Sambalpur/Jharsuguda)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>17670369</t>
+          <t>18306349</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>GEM/2026/B/7435893</t>
+          <t>2026_NTPC_111933_1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>handling service, excavator with crusher bucket system with screening and loading of coal into tippers at kusmunda oc kusmunda area</t>
+          <t>transportation of 2 lmt coal from nlc talabira mines to ntpc simhadri through rcr mode - as per sow</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Loading / handling / crushing</t>
+          <t>Coal transport (RCR / siding)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>South Eastern Coalfields Limited</t>
+          <t>National Thermal Power Corporation Limited</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4171,30 +4182,31 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Korba</t>
+          <t>Raipur</t>
         </is>
       </c>
       <c r="O35" s="5" t="n">
-        <v>46156</v>
+        <v>46288</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>AOC</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Fsnl Private Limited, Maa Sarwamangla Transport Company</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Anoop Road Carriers, Bharat Road Carrier, Mohit Minerals, Sangita Sales</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr">
         <is>
           <t>5 named / 8</t>
         </is>
-      </c>
-      <c r="T35" t="n">
-        <v>24.94</v>
       </c>
       <c r="U35" s="6">
         <f>IF(ISNUMBER(G35),MAX(MAX(G35,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -4221,51 +4233,51 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>mine = coal company's tender city; siding = same area</t>
+          <t>mine named in title; plant/siding named in title</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Korba (tender city)</t>
+          <t>Talabira (near Sambalpur/Jharsuguda)</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Korba (tender city)</t>
+          <t>Talabira (near Sambalpur/Jharsuguda)</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G36" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>15659451</t>
+          <t>18286732</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6627991</t>
+          <t>2026_NTPC_111957_1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>handling service, transpor</t>
+          <t>coal transportation from nlc talabira mines to ntpc telangana(ttgr) - coal transportation from nlc talabira mines to ntpc telangana(ttgr)through rcr mode</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Loading / handling / crushing</t>
+          <t>Coal transport (RCR / siding)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>South Eastern Coalfields Limited</t>
+          <t>National Thermal Power Corporation Limited</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4275,11 +4287,11 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Korba</t>
+          <t>Raipur</t>
         </is>
       </c>
       <c r="O36" s="5" t="n">
-        <v>45923</v>
+        <v>46287</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -4288,21 +4300,21 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Harsh Roadlines Private Limited</t>
+          <t>Swami Fuels Private Limited</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Orissa Stevedores</t>
+          <t>Anoop Road Carriers, Swami Fuels, Tirupati Minerals</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>5 named / 8</t>
+          <t>4 named / 4</t>
         </is>
       </c>
       <c r="T36" t="n">
-        <v>82.78</v>
+        <v>6.68</v>
       </c>
       <c r="U36" s="6">
         <f>IF(ISNUMBER(G36),MAX(MAX(G36,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -4329,65 +4341,58 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>mine = coal company's tender city; siding = same area</t>
+          <t>mine named in title</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Korba (tender city)</t>
+          <t>Talabira (near Sambalpur/Jharsuguda)</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>88</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Korba (tender city)</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>88</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>17304517</t>
+          <t>18222478</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>GEM/2026/B/7372908</t>
+          <t>2026_NTPC_111805_1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>handling service, transport service, handling &amp; transport service, ob removal, composite work for ob removal coal cutting by surface miner and loading and transportation of coal..</t>
+          <t>coal transportation from nlc talabira mines to ntpc kudgi through rcr</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Mining services (OB / extraction)</t>
+          <t>Coal transport (RCR / siding)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>South Eastern Coalfields Limited</t>
+          <t>National Thermal Power Corporation Limited</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Korba</t>
+          <t>Kudligi</t>
         </is>
       </c>
       <c r="O37" s="5" t="n">
-        <v>46135</v>
+        <v>46156</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -4396,17 +4401,17 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Knr Constructions Limited</t>
+          <t>Kalyani Ventures Limited</t>
         </is>
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>5 named / 8</t>
+          <t>1 named / 1</t>
         </is>
       </c>
       <c r="T37" t="n">
-        <v>3966.12</v>
+        <v>1.5</v>
       </c>
       <c r="U37" s="6">
         <f>IF(ISNUMBER(G37),MAX(MAX(G37,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -4433,77 +4438,78 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>mine named in title</t>
+          <t>mine named in title; plant = tender city in West Bengal</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Korba</t>
+          <t>Talabira (near Sambalpur/Jharsuguda)</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>16765105</t>
+          <t>15407506</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>GEM/2025/B/7003673</t>
+          <t>2025_DVC_245419_1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>ob removal, handling &amp; transport service, hiring of hemm for ob removal and coal drilling with loading and transportation at manikpur ocp korba area</t>
+          <t>lifting of 20.0(twenty) lmt coal from nlc india limited (nlcil)-talabira ii and iii ocp, sambalpur, odisha to dstps and other tps of dvc through rcr mode</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Mining services (OB / extraction)</t>
+          <t>Coal transport (RCR / siding)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>South Eastern Coalfields Limited</t>
+          <t>Damodar Valley Corporation</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Korba</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="O38" s="5" t="n">
-        <v>46043</v>
+        <v>45897</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>AOC</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Orissa Stevedores Limited</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Anoop Road Carriers, Godavari Commodities</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>5 named / 10</t>
-        </is>
-      </c>
-      <c r="T38" t="n">
-        <v>1775.85</v>
+          <t>5 named / 17</t>
+        </is>
       </c>
       <c r="U38" s="6">
         <f>IF(ISNUMBER(G38),MAX(MAX(G38,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -4530,84 +4536,78 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mine = coal company's tender city; siding = same area</t>
+          <t>mine named in title</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Korba (tender city)</t>
+          <t>Talabira (near Sambalpur/Jharsuguda)</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>88</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Korba (tender city)</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>88</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>16245601</t>
+          <t>14761261</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6729097</t>
+          <t>2025_NTPC_98583_1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>hiring of pay loader incorporated with weight sensors for mechanical transfer of coal into railway wagons for a quantity of 17520000 te with minimum tpd16000 te for a period of ..</t>
+          <t>transportation of 300000mt coal from nlc talabira mines of nlc ltd to ntpc simhadri under rcr mode through any nearby siding</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Coal transport (RCR / siding)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>South Eastern Coalfields Limited</t>
+          <t>National Thermal Power Corporation Limited</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Korba</t>
+          <t>Visakhapatnam</t>
         </is>
       </c>
       <c r="O39" s="5" t="n">
-        <v>45948</v>
+        <v>45880</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>AOC</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Sat Kartar Logistics</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Advika Logistics, Anoop Road Carriers, Indermani / Indramani</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>5 named / 19</t>
-        </is>
-      </c>
-      <c r="T39" t="n">
-        <v>14.89</v>
+          <t>5 named / 15</t>
+        </is>
       </c>
       <c r="U39" s="6">
         <f>IF(ISNUMBER(G39),MAX(MAX(G39,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -4639,60 +4639,60 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Korba (tender city)</t>
+          <t>Sambalpur (tender city)</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Korba (tender city)</t>
+          <t>Sambalpur (tender city)</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="G40" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>12743621</t>
+          <t>12395907</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>GEM/2025/B/5926593</t>
+          <t>GEM/2024/B/5759091</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>hiring of payloaders and t</t>
+          <t>coal loading and transport</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Coal transport (road)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>South Eastern Coalfields Limited</t>
+          <t>Mahanadi Coalfields Limited</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Orissa</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Korba</t>
+          <t>Sambalpur</t>
         </is>
       </c>
       <c r="O40" s="5" t="n">
-        <v>45712</v>
+        <v>45670</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -4701,17 +4701,17 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Harsh Roadlines Private Limited</t>
+          <t>Vlt Associates</t>
         </is>
       </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>5 named / 7</t>
+          <t>5 named / 10</t>
         </is>
       </c>
       <c r="T40" t="n">
-        <v>2.41</v>
+        <v>28</v>
       </c>
       <c r="U40" s="6">
         <f>IF(ISNUMBER(G40),MAX(MAX(G40,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="G41" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="G42" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -4971,10 +4971,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G43" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G44" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -5179,11 +5179,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G46" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -5380,11 +5380,11 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G48" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -5585,11 +5585,11 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G50" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -5795,10 +5795,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G51" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G52" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -5996,11 +5996,11 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -6093,11 +6093,11 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -6202,10 +6202,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G55" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -6293,78 +6293,81 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>plant = tender city</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Rourkela (tender city)</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
+          <t>mine named in title</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Baikunthpur / Chirimiri (Korea)</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>156</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="G56" t="n">
         <v>156</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>18282487</t>
+          <t>17026374</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>GEM/2026/B/7469992</t>
+          <t>GEM/2026/B/7088635</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>lifting of of coal from mcl mines (kuldabelpaharlajkuralakhanpursamaleswerigarjanbaha l) to any railway sidinggoods shed private siding ( ser,secr,east coast railways) under rcr mode &amp; supervison of c</t>
+          <t>handling service, handling &amp; transport service, transport service, hiring of tippers for transportation of coal and loading of coal at ncph r6 mine at chirimiri area</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Coal transport (RCR / siding)</t>
+          <t>Coal transport (road)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Ntpc-Sail Power Company Private Limited</t>
+          <t>South Eastern Coalfields Limited</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Orissa</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Rourkela</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="O56" s="5" t="n">
-        <v>46206</v>
+        <v>46046</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AOC</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nakul Tiwari</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Anoop Road Carriers, Bharat Road Carrier</t>
+          <t>G K Associates, Chandan Kumar Singh</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>5 named / 12</t>
-        </is>
+          <t>5 named / 6</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
+        <v>7.23</v>
       </c>
       <c r="U56" s="6">
         <f>IF(ISNUMBER(G56),MAX(MAX(G56,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -6391,13 +6394,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>plant/siding named in title</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>mine = coal company's tender city; siding = same area</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>156</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rourkela</t>
+          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -6408,61 +6418,60 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>16080231</t>
+          <t>14761654</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>GEM/2025/B/7016181</t>
+          <t>GEM/2025/B/6531525</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>short term one time coal shifting from dsp beds to nspcl coal yard,pp-ii and pp-iii</t>
+          <t>coal transportation from k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Loading / handling / crushing</t>
+          <t>Coal transport (road)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Ntpc-Sail Power Company Private Limited</t>
+          <t>South Eastern Coalfields Limited</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Durgapur</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="O57" s="5" t="n">
-        <v>46020</v>
+        <v>45883</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AOC</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>United Coal Carriers</t>
-        </is>
-      </c>
+          <t>Ajay Shrivas</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>5 named / 6</t>
-        </is>
+          <t>3 named / 3</t>
+        </is>
+      </c>
+      <c r="T57" t="n">
+        <v>0.41</v>
       </c>
       <c r="U57" s="6">
         <f>IF(ISNUMBER(G57),MAX(MAX(G57,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -6489,58 +6498,58 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>plant/siding named in title</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Rourkela</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
+          <t>mine named in title</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Baikunthpur / Chirimiri (Korea)</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
         <v>156</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="G58" t="n">
         <v>156</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>13548763</t>
+          <t>14370610</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6130476</t>
+          <t>GEM/2025/B/6354284</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>coal shifting from dsp beds to nspcl coal yard of chp pp-ii and iii(ssc/2</t>
+          <t>handling ,transport and other mining services - percentagequote based - handling &amp; transport service, loading andtransportation of coal at rani atari chirimiri area</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Loading / handling / crushing</t>
+          <t>Coal transport (road)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Ntpc-Sail Power Company Private Limited</t>
+          <t>South Eastern Coalfields Limited</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Durgapur</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="O58" s="5" t="n">
-        <v>45792</v>
+        <v>45845</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -6549,21 +6558,17 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Phoenix Solutions</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>Nkas Services</t>
-        </is>
-      </c>
+          <t>G K Associates</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>5 named / 5</t>
+          <t>5 named / 29</t>
         </is>
       </c>
       <c r="T58" t="n">
-        <v>1.63</v>
+        <v>81.11</v>
       </c>
       <c r="U58" s="6">
         <f>IF(ISNUMBER(G58),MAX(MAX(G58,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -6590,13 +6595,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>plant/siding named in title</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>mine = coal company's tender city; siding = same area</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>156</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rourkela</t>
+          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -6607,41 +6619,41 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>12298393</t>
+          <t>13712378</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>GEM/2024/B/5717697</t>
+          <t>GEM/2025/B/6218223</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>coal shifting from dsp beds to nspcl coal yard of chp ppii and iii for 3</t>
+          <t>handling &amp; transport servi</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Loading / handling / crushing</t>
+          <t>Coal transport (road)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Ntpc-Sail Power Company Private Limited</t>
+          <t>South Eastern Coalfields Limited</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Durgapur</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="O59" s="5" t="n">
-        <v>45658</v>
+        <v>45803</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -6650,21 +6662,21 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>M/S United Coal Carriers</t>
+          <t>Dadan Singh Llp</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>United Coal Carriers</t>
+          <t>G K Associates, Chandan Kumar Singh</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>4 named / 4</t>
+          <t>5 named / 7</t>
         </is>
       </c>
       <c r="T59" t="n">
-        <v>0.85</v>
+        <v>7.05</v>
       </c>
       <c r="U59" s="6">
         <f>IF(ISNUMBER(G59),MAX(MAX(G59,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -6691,34 +6703,41 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>mine named in title</t>
+          <t>mine = coal company's tender city; siding = same area</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Baikunthpur / Chirimiri (Korea)</t>
+          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>174</v>
-      </c>
-      <c r="E60" t="inlineStr"/>
+        <v>156</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>156</v>
+      </c>
       <c r="G60" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>17026374</t>
+          <t>13609214</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>GEM/2026/B/7088635</t>
+          <t>GEM/2025/B/6201579</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>handling service, handling &amp; transport service, transport service, hiring of tippers for transportation of coal and loading of coal at ncph r6 mine at chirimiri area</t>
+          <t>loading and transportation</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6742,7 +6761,7 @@
         </is>
       </c>
       <c r="O60" s="5" t="n">
-        <v>46046</v>
+        <v>45798</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -6751,21 +6770,21 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Nakul Tiwari</t>
+          <t>M/S Ramesh Kumar Agrawal And Sons</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>G K Associates, Chandan Kumar Singh</t>
+          <t>G K Associates</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>5 named / 6</t>
+          <t>5 named / 10</t>
         </is>
       </c>
       <c r="T60" t="n">
-        <v>7.23</v>
+        <v>7</v>
       </c>
       <c r="U60" s="6">
         <f>IF(ISNUMBER(G60),MAX(MAX(G60,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -6801,7 +6820,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -6809,24 +6828,24 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="G61" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>14761654</t>
+          <t>13485534</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6531525</t>
+          <t>GEM/2025/B/6155880</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>coal transportation from k</t>
+          <t>handling &amp; transport servi</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6850,7 +6869,7 @@
         </is>
       </c>
       <c r="O61" s="5" t="n">
-        <v>45883</v>
+        <v>45784</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -6859,17 +6878,17 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Ajay Shrivas</t>
+          <t>M/S Chandan Kumar Singh</t>
         </is>
       </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>3 named / 3</t>
+          <t>5 named / 8</t>
         </is>
       </c>
       <c r="T61" t="n">
-        <v>0.41</v>
+        <v>5.33</v>
       </c>
       <c r="U61" s="6">
         <f>IF(ISNUMBER(G61),MAX(MAX(G61,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -6896,34 +6915,41 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>mine named in title</t>
+          <t>mine = coal company's tender city; siding = same area</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Baikunthpur / Chirimiri (Korea)</t>
+          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>174</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
+        <v>156</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>156</v>
+      </c>
       <c r="G62" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>14370610</t>
+          <t>13513655</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6354284</t>
+          <t>GEM/2025/B/6174810</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>handling ,transport and other mining services - percentagequote based - handling &amp; transport service, loading andtransportation of coal at rani atari chirimiri area</t>
+          <t>coal transportation from k</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6947,7 +6973,7 @@
         </is>
       </c>
       <c r="O62" s="5" t="n">
-        <v>45845</v>
+        <v>45783</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -6956,17 +6982,17 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>G K Associates</t>
+          <t>Harsh Roadlines Private Limited</t>
         </is>
       </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>5 named / 29</t>
+          <t>4 named / 4</t>
         </is>
       </c>
       <c r="T62" t="n">
-        <v>81.11</v>
+        <v>0.41</v>
       </c>
       <c r="U62" s="6">
         <f>IF(ISNUMBER(G62),MAX(MAX(G62,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -7002,7 +7028,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -7010,29 +7036,29 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="G63" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>13712378</t>
+          <t>13180185</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6218223</t>
+          <t>GEM/2025/B/6070928</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>handling &amp; transport servi</t>
+          <t>hiring of payloader for lo</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Coal transport (road)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -7051,7 +7077,7 @@
         </is>
       </c>
       <c r="O63" s="5" t="n">
-        <v>45803</v>
+        <v>45751</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -7060,21 +7086,21 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Dadan Singh Llp</t>
+          <t>G K Associates</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>G K Associates, Chandan Kumar Singh</t>
+          <t>G K Associates</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>5 named / 7</t>
+          <t>5 named / 14</t>
         </is>
       </c>
       <c r="T63" t="n">
-        <v>7.05</v>
+        <v>37.74</v>
       </c>
       <c r="U63" s="6">
         <f>IF(ISNUMBER(G63),MAX(MAX(G63,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -7110,7 +7136,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -7118,29 +7144,29 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="G64" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>13609214</t>
+          <t>13097848</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6201579</t>
+          <t>GEM/2025/B/6038225</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>loading and transportation</t>
+          <t>hiring of pay loader for l</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Coal transport (road)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -7159,7 +7185,7 @@
         </is>
       </c>
       <c r="O64" s="5" t="n">
-        <v>45798</v>
+        <v>45740</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -7168,7 +7194,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>M/S Ramesh Kumar Agrawal And Sons</t>
+          <t>G K Associates, M/S Ramesh Kumar Agrawal And Sons, Vivek Construction</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -7178,11 +7204,11 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>5 named / 10</t>
+          <t>5 named / 17</t>
         </is>
       </c>
       <c r="T64" t="n">
-        <v>7</v>
+        <v>25.16</v>
       </c>
       <c r="U64" s="6">
         <f>IF(ISNUMBER(G64),MAX(MAX(G64,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -7209,20 +7235,13 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>mine = coal company's tender city; siding = same area</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>174</v>
-      </c>
+          <t>plant = tender city</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
+          <t>Rourkela (tender city)</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -7233,60 +7252,61 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>13485534</t>
+          <t>18282487</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6155880</t>
+          <t>GEM/2026/B/7469992</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>handling &amp; transport servi</t>
+          <t>lifting of of coal from mcl mines (kuldabelpaharlajkuralakhanpursamaleswerigarjanbaha l) to any railway sidinggoods shed private siding ( ser,secr,east coast railways) under rcr mode &amp; supervison of c</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Coal transport (road)</t>
+          <t>Coal transport (RCR / siding)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>South Eastern Coalfields Limited</t>
+          <t>Ntpc-Sail Power Company Private Limited</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Orissa</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Rourkela</t>
         </is>
       </c>
       <c r="O65" s="5" t="n">
-        <v>45784</v>
+        <v>46206</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>AOC</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>M/S Chandan Kumar Singh</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Anoop Road Carriers, Bharat Road Carrier</t>
+        </is>
+      </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>5 named / 8</t>
-        </is>
-      </c>
-      <c r="T65" t="n">
-        <v>5.33</v>
+          <t>5 named / 12</t>
+        </is>
       </c>
       <c r="U65" s="6">
         <f>IF(ISNUMBER(G65),MAX(MAX(G65,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -7313,20 +7333,13 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>mine = coal company's tender city; siding = same area</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>174</v>
-      </c>
+          <t>plant/siding named in title</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
+          <t>Rourkela</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -7337,60 +7350,61 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>13513655</t>
+          <t>16080231</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6174810</t>
+          <t>GEM/2025/B/7016181</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>coal transportation from k</t>
+          <t>short term one time coal shifting from dsp beds to nspcl coal yard,pp-ii and pp-iii</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Coal transport (road)</t>
+          <t>Loading / handling / crushing</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>South Eastern Coalfields Limited</t>
+          <t>Ntpc-Sail Power Company Private Limited</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Durgapur</t>
         </is>
       </c>
       <c r="O66" s="5" t="n">
-        <v>45783</v>
+        <v>46020</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>AOC</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Harsh Roadlines Private Limited</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>United Coal Carriers</t>
+        </is>
+      </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>4 named / 4</t>
-        </is>
-      </c>
-      <c r="T66" t="n">
-        <v>0.41</v>
+          <t>5 named / 6</t>
+        </is>
       </c>
       <c r="U66" s="6">
         <f>IF(ISNUMBER(G66),MAX(MAX(G66,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -7417,20 +7431,13 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>mine = coal company's tender city; siding = same area</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>174</v>
-      </c>
+          <t>plant/siding named in title</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
+          <t>Rourkela</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -7441,41 +7448,41 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>13180185</t>
+          <t>13548763</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6070928</t>
+          <t>GEM/2025/B/6130476</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>hiring of payloader for lo</t>
+          <t>coal shifting from dsp beds to nspcl coal yard of chp pp-ii and iii(ssc/2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Loading / handling / crushing</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>South Eastern Coalfields Limited</t>
+          <t>Ntpc-Sail Power Company Private Limited</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Durgapur</t>
         </is>
       </c>
       <c r="O67" s="5" t="n">
-        <v>45751</v>
+        <v>45792</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -7484,21 +7491,21 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>G K Associates</t>
+          <t>Phoenix Solutions</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>G K Associates</t>
+          <t>Nkas Services</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>5 named / 14</t>
+          <t>5 named / 5</t>
         </is>
       </c>
       <c r="T67" t="n">
-        <v>37.74</v>
+        <v>1.63</v>
       </c>
       <c r="U67" s="6">
         <f>IF(ISNUMBER(G67),MAX(MAX(G67,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -7525,20 +7532,13 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>mine = coal company's tender city; siding = same area</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>174</v>
-      </c>
+          <t>plant/siding named in title</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Baikunthpur / Chirimiri (Korea) (tender city)</t>
+          <t>Rourkela</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -7549,41 +7549,41 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>13097848</t>
+          <t>12298393</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>GEM/2025/B/6038225</t>
+          <t>GEM/2024/B/5717697</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>hiring of pay loader for l</t>
+          <t>coal shifting from dsp beds to nspcl coal yard of chp ppii and iii for 3</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Loading / handling / crushing</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>South Eastern Coalfields Limited</t>
+          <t>Ntpc-Sail Power Company Private Limited</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Durgapur</t>
         </is>
       </c>
       <c r="O68" s="5" t="n">
-        <v>45740</v>
+        <v>45658</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -7592,21 +7592,21 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>G K Associates, M/S Ramesh Kumar Agrawal And Sons, Vivek Construction</t>
+          <t>M/S United Coal Carriers</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>G K Associates</t>
+          <t>United Coal Carriers</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>5 named / 17</t>
+          <t>4 named / 4</t>
         </is>
       </c>
       <c r="T68" t="n">
-        <v>25.16</v>
+        <v>0.85</v>
       </c>
       <c r="U68" s="6">
         <f>IF(ISNUMBER(G68),MAX(MAX(G68,Settings!$B$13)*Settings!$B$7*Settings!$B$5,IF(ISNUMBER(Settings!$B$12),Settings!$B$12,0))*(1+IF(Settings!$B$11="Y",0,Settings!$B$10/100))+N(Settings!$B$9),"")</f>
@@ -7642,11 +7642,11 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G70" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G71" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -7939,10 +7939,10 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G72" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G81" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G82" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -8965,10 +8965,10 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G83" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -9073,10 +9073,10 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G84" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -9177,10 +9177,10 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G85" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G86" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -9389,10 +9389,10 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G87" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -9486,10 +9486,10 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G88" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G89" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -9702,10 +9702,10 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="G90" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -30694,12 +30694,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Raigarh town (siding station not yet given)</t>
+          <t>Chaple, Kharsia block, Raigarh district (VWLR siding; Open-Meteo geocode 2026-10-12; Aman: Chaple is 1.2 km from the Vedanta substation)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Give me your siding's railway station and I will re-run from it.</t>
+          <t>Chaple, Kharsia (VWLR). Town-centre geocode; siding is within about 1-2 km of it.</t>
         </is>
       </c>
     </row>
